--- a/Дело3а-78-2026Таганай/05_ЕКЖЯ/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/05_ЕКЖЯ/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92994225494</v>
+        <v>46157.93082085858</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/05_ЕКЖЯ/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/05_ЕКЖЯ/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93082085858</v>
+        <v>46157.93352698476</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/05_ЕКЖЯ/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/05_ЕКЖЯ/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93352698476</v>
+        <v>46157.93640827757</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/05_ЕКЖЯ/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/05_ЕКЖЯ/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93640827757</v>
+        <v>46158.28177859476</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/05_ЕКЖЯ/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/05_ЕКЖЯ/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28177859476</v>
+        <v>46158.29754354763</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
@@ -787,7 +787,7 @@
         <v>6.7</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>46157.92961568389</v>
+        <v>46158.29718733217</v>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>46157.37863312778</v>
       </c>
       <c r="H5" s="16" t="n">
-        <v>46157.92961568389</v>
+        <v>46158.29718733217</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/05_ЕКЖЯ/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/05_ЕКЖЯ/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29754354763</v>
+        <v>46158.29772610644</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/05_ЕКЖЯ/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/05_ЕКЖЯ/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29772610644</v>
+        <v>46158.30446464708</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/05_ЕКЖЯ/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/05_ЕКЖЯ/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.30446464708</v>
+        <v>46158.33341278171</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/05_ЕКЖЯ/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/05_ЕКЖЯ/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33341278171</v>
+        <v>46158.37202041309</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/05_ЕКЖЯ/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/05_ЕКЖЯ/Сводная_ведомость.xlsx
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37202041309</v>
+        <v>46158.37417809882</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
@@ -787,7 +787,7 @@
         <v>6.7</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>46158.29718733217</v>
+        <v>46158.37374795885</v>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>46157.37863312778</v>
       </c>
       <c r="H5" s="16" t="n">
-        <v>46158.29718733217</v>
+        <v>46158.37374795885</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
